--- a/master-db/volkswagen.xlsx
+++ b/master-db/volkswagen.xlsx
@@ -64,7 +64,7 @@
     <t/>
   </si>
   <si>
-    <t>대기</t>
+    <t>완료</t>
   </si>
   <si>
     <t>디젤 2WD</t>
